--- a/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S14_Required_Approvals_Federal_Tribal_Corporate_Landowner_Lender.xlsx
+++ b/Lumbee_RIVR_TBCP_Agreement_Package/05_Schedules/S14_Required_Approvals_Federal_Tribal_Corporate_Landowner_Lender.xlsx
@@ -532,6 +532,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”); LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”); Lumbee River Electric Membership Corporation d/b/a Lumbee River EMC (“LREMC”), separate asset owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -646,6 +654,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
